--- a/site/public/downloads/ken/ken-business.xlsx
+++ b/site/public/downloads/ken/ken-business.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>台灣個人／家庭通膨每年 10% 起跳。官方 CPI 約 2% 左右，但房租、外食、醫療與照護的實際漲幅常遠高於 CPI；本工具採保守的 10% 起跳假設，讓規劃留足安全邊際。通膨格子設有驗證，低於 10% 會被拒絕，公式也以 MAX(10%, 輸入值) 計算。</t>
+          <t>台灣個人／家庭通膨每年 5% 起跳。官方 CPI 約 2% 左右，但房租、外食、醫療與照護的實際漲幅常遠高於 CPI；本工具採保守的 5% 起跳假設，讓規劃留足安全邊際。通膨格子設有驗證，低於 5% 會被拒絕，公式也以 MAX(5%, 輸入值) 計算。</t>
         </is>
       </c>
     </row>
@@ -779,15 +779,15 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -1026,27 +1026,27 @@
         </is>
       </c>
       <c r="B20" s="13">
-        <f>(B15+B16+B17)*IF($B$10=1,(1+MAX(0.1,$B$9))^((1-1)/12),1)+B18+$B$8</f>
+        <f>(B15+B16+B17)*IF($B$10=1,(1+MAX(0.05,$B$9))^((1-1)/12),1)+B18+$B$8</f>
         <v/>
       </c>
       <c r="C20" s="13">
-        <f>(C15+C16+C17)*IF($B$10=1,(1+MAX(0.1,$B$9))^((2-1)/12),1)+C18</f>
+        <f>(C15+C16+C17)*IF($B$10=1,(1+MAX(0.05,$B$9))^((2-1)/12),1)+C18</f>
         <v/>
       </c>
       <c r="D20" s="13">
-        <f>(D15+D16+D17)*IF($B$10=1,(1+MAX(0.1,$B$9))^((3-1)/12),1)+D18</f>
+        <f>(D15+D16+D17)*IF($B$10=1,(1+MAX(0.05,$B$9))^((3-1)/12),1)+D18</f>
         <v/>
       </c>
       <c r="E20" s="13">
-        <f>(E15+E16+E17)*IF($B$10=1,(1+MAX(0.1,$B$9))^((4-1)/12),1)+E18</f>
+        <f>(E15+E16+E17)*IF($B$10=1,(1+MAX(0.05,$B$9))^((4-1)/12),1)+E18</f>
         <v/>
       </c>
       <c r="F20" s="13">
-        <f>(F15+F16+F17)*IF($B$10=1,(1+MAX(0.1,$B$9))^((5-1)/12),1)+F18</f>
+        <f>(F15+F16+F17)*IF($B$10=1,(1+MAX(0.05,$B$9))^((5-1)/12),1)+F18</f>
         <v/>
       </c>
       <c r="G20" s="13">
-        <f>(G15+G16+G17)*IF($B$10=1,(1+MAX(0.1,$B$9))^((6-1)/12),1)+G18</f>
+        <f>(G15+G16+G17)*IF($B$10=1,(1+MAX(0.05,$B$9))^((6-1)/12),1)+G18</f>
         <v/>
       </c>
     </row>
@@ -1175,8 +1175,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1267,15 +1267,15 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="B16" s="14">
-        <f>IF($B$5-$B$6*(1+MAX(0.1,$B$9))&gt;0,ROUNDUP($B$4/($B$5-$B$6*(1+MAX(0.1,$B$9))),0),"虧損")</f>
+        <f>IF($B$5-$B$6*(1+MAX(0.05,$B$9))&gt;0,ROUNDUP($B$4/($B$5-$B$6*(1+MAX(0.05,$B$9))),0),"虧損")</f>
         <v/>
       </c>
     </row>
@@ -1504,8 +1504,8 @@
     <mergeCell ref="A2:E2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1985,15 +1985,15 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="B8" s="18">
-        <f>MAX(0.1,$B$6)</f>
+        <f>MAX(0.05,$B$6)</f>
         <v/>
       </c>
     </row>
@@ -2280,8 +2280,8 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2382,15 +2382,15 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>個人／家庭通膨（10% 起跳）</t>
+          <t>個人／家庭通膨（5% 起跳）</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>不可低於 10%</t>
+          <t>不可低於 5%</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="B14" s="14">
-        <f>$B$9*(1+MAX(0.1,$B$10))+$B$12-$B$13</f>
+        <f>$B$9*(1+MAX(0.05,$B$10))+$B$12-$B$13</f>
         <v/>
       </c>
     </row>
@@ -2462,8 +2462,8 @@
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"一般,優惠A,優惠B"</formula1>
     </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 10% 起跳，請輸入 10% 以上。" type="decimal" operator="greaterThanOrEqual">
-      <formula1>0.1</formula1>
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="通膨假設" error="本工具假設台灣個人通膨每年 5% 起跳，請輸入 5% 以上。" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0.05</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
